--- a/Results/Summarized Result.xlsx
+++ b/Results/Summarized Result.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahbub\Documents\GitHub\EnergyPLANDomainKnowledgeEAStep1\Results\truePf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahbub\Documents\GitHub\EnergyPLANDomainKnowledgeEAStep1\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
   <si>
     <t>SBX_POLY</t>
   </si>
@@ -85,10 +85,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,30 +393,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="0.85546875" customWidth="1"/>
     <col min="14" max="14" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -463,16 +463,19 @@
         <v>3</v>
       </c>
       <c r="R2" t="s">
+        <v>4</v>
+      </c>
+      <c r="S2" t="s">
         <v>5</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>7</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>365652</v>
       </c>
@@ -482,7 +485,7 @@
       <c r="C3">
         <v>3.7168348676272999E-3</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>5.6150322950234699E-3</v>
       </c>
       <c r="E3">
@@ -521,23 +524,27 @@
         <v>1</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R12" si="0">IF(L3&lt;E3,1,-1)</f>
-        <v>-1</v>
+        <f t="shared" ref="R3:S12" si="0">IF(K3&lt;D3,1,-1)</f>
+        <v>1</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S12" si="1">IF(M3&lt;F3,1,-1)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>-1</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T12" si="2">IF(N3&lt;G3,1,-1)</f>
+        <f t="shared" ref="T3:T12" si="1">IF(M3&lt;F3,1,-1)</f>
         <v>1</v>
       </c>
       <c r="U3">
-        <f>SUM(P3:T3)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" ref="U3:U12" si="2">IF(N3&lt;G3,1,-1)</f>
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <f>SUM(P3:U3)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>455875</v>
       </c>
@@ -547,7 +554,7 @@
       <c r="C4">
         <v>6.7040071436758903E-3</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>6.4067474959280204E-4</v>
       </c>
       <c r="E4">
@@ -590,19 +597,23 @@
         <v>-1</v>
       </c>
       <c r="S4">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="T4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U4">
-        <f t="shared" ref="U4:U12" si="4">SUM(P4:T4)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V4">
+        <f t="shared" ref="V4:V12" si="4">SUM(P4:U4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>456545</v>
       </c>
@@ -612,8 +623,8 @@
       <c r="C5">
         <v>1.8590935387607099E-3</v>
       </c>
-      <c r="D5" s="1">
-        <v>6.4067474959280204E-4</v>
+      <c r="D5" s="2">
+        <v>8.1112960450058604E-4</v>
       </c>
       <c r="E5">
         <v>0.67553809179623603</v>
@@ -652,22 +663,26 @@
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T5">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <f t="shared" si="4"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>458478</v>
       </c>
@@ -677,7 +692,7 @@
       <c r="C6">
         <v>7.3532440798551799E-3</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>2.5390048333201101E-3</v>
       </c>
       <c r="E6">
@@ -717,22 +732,26 @@
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>545782</v>
       </c>
@@ -742,7 +761,7 @@
       <c r="C7">
         <v>2.6965517951551199E-3</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>5.7802776854334499E-3</v>
       </c>
       <c r="E7">
@@ -785,19 +804,23 @@
         <v>1</v>
       </c>
       <c r="S7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>547945</v>
       </c>
@@ -807,7 +830,7 @@
       <c r="C8">
         <v>6.9594158057584904E-3</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>1.58209669779739E-3</v>
       </c>
       <c r="E8">
@@ -847,22 +870,26 @@
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T8">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>549235</v>
       </c>
@@ -872,7 +899,7 @@
       <c r="C9">
         <v>3.7960067642293801E-3</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>5.6171149335229901E-3</v>
       </c>
       <c r="E9">
@@ -912,22 +939,26 @@
       </c>
       <c r="R9">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S9">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="T9">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <f t="shared" si="4"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>562366</v>
       </c>
@@ -937,7 +968,7 @@
       <c r="C10">
         <v>6.72549250934509E-3</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="2">
         <v>4.8877902792603296E-4</v>
       </c>
       <c r="E10">
@@ -977,22 +1008,26 @@
       </c>
       <c r="R10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T10">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>652262</v>
       </c>
@@ -1002,7 +1037,7 @@
       <c r="C11">
         <v>7.7839014080908096E-3</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>2.2673483150736501E-3</v>
       </c>
       <c r="E11">
@@ -1045,19 +1080,23 @@
         <v>-1</v>
       </c>
       <c r="S11">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="T11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>981354</v>
       </c>
@@ -1067,7 +1106,7 @@
       <c r="C12">
         <v>3.4111505553262199E-3</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>2.6263581741608E-3</v>
       </c>
       <c r="E12">
@@ -1107,22 +1146,26 @@
       </c>
       <c r="R12">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T12">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="P13">
         <f>SUM(P3:P12)</f>
         <v>-2</v>
@@ -1133,37 +1176,41 @@
       </c>
       <c r="R13">
         <f>SUM(R3:R12)</f>
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="S13">
         <f>SUM(S3:S12)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13">
         <f>SUM(T3:T12)</f>
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <f>SUM(U3:U12)</f>
         <v>8</v>
       </c>
-      <c r="U13">
-        <f>SUM(P13:T13)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S15">
+      <c r="V13">
+        <f>SUM(P13:U13)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T15">
         <v>17</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <f>17/50*100</f>
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="S16">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T16">
         <f>50-17</f>
         <v>33</v>
       </c>
-      <c r="T16">
-        <f>S16/50*100</f>
+      <c r="U16">
+        <f>T16/50*100</f>
         <v>66</v>
       </c>
     </row>
